--- a/Relatorio/Relatorio_Dados.xlsx
+++ b/Relatorio/Relatorio_Dados.xlsx
@@ -1,19 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\paulo\Desktop\Relatório_PI\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\ESTG 25_26\2S\ProjetoInformatico\Prototipo\Versoes\weatherSense\Relatorio\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A2CC327F-1E77-485C-9885-EEC0523A2976}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D5292D7-D474-4A4A-B5F7-82536FF9C8A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Folha1" sheetId="1" r:id="rId1"/>
+    <sheet name="Req_tests" sheetId="1" r:id="rId1"/>
+    <sheet name="Ambiente de Testes" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -25,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="179" uniqueCount="161">
   <si>
     <t>Objetivo</t>
   </si>
@@ -48,137 +49,473 @@
     <t>Disponibilizar observações meteorológicas</t>
   </si>
   <si>
-    <t>Observações apresentadas corretamente</t>
-  </si>
-  <si>
-    <t>Consulta de observações em várias localizações</t>
-  </si>
-  <si>
-    <t>Captura de ecrã</t>
-  </si>
-  <si>
     <t>Capturas de ecrã</t>
   </si>
   <si>
     <t>Disponibilizar previsões terrestres</t>
   </si>
   <si>
-    <t>Previsões apresentadas corretamente</t>
-  </si>
-  <si>
-    <t>Consulta de previsões terrestres</t>
-  </si>
-  <si>
     <t>Disponibilizar previsões marítimas</t>
   </si>
   <si>
-    <t>Consulta de previsões marítimas</t>
-  </si>
-  <si>
     <t>Disponibilizar histórico</t>
   </si>
   <si>
-    <t>Dados históricos acessíveis</t>
-  </si>
-  <si>
-    <t>Consulta de registos históricos</t>
-  </si>
-  <si>
     <t>Comparar fontes</t>
   </si>
   <si>
-    <t>Informação apresentada lado a lado</t>
-  </si>
-  <si>
-    <t>Comparação da mesma localização</t>
-  </si>
-  <si>
     <t>Garantir desempenho adequado</t>
   </si>
   <si>
-    <t>Tabelas e gráficos</t>
-  </si>
-  <si>
-    <t>Execução repetida de pedidos aos endpoints</t>
-  </si>
-  <si>
-    <t>Latência média, mínima e máxima</t>
-  </si>
-  <si>
-    <t>Consulta realizada com sucesso</t>
-  </si>
-  <si>
-    <t>Número de fontes apresentadas</t>
-  </si>
-  <si>
-    <t>Capturas de ecrã e resultados da consulta</t>
-  </si>
-  <si>
-    <t>Os pedidos são processados em tempo aceitável</t>
-  </si>
-  <si>
     <t>Validar normalização dos dados</t>
   </si>
   <si>
-    <t>Dados seguem a estrutura definida</t>
-  </si>
-  <si>
-    <t>Comparar resposta original da API com dados normalizados</t>
-  </si>
-  <si>
-    <t>Campos normalizados corretamente</t>
-  </si>
-  <si>
-    <t>Exemplo de dados antes/depois</t>
-  </si>
-  <si>
     <t>Armazenar dados meteorológicos</t>
   </si>
   <si>
-    <t>Dados guardados após recolha</t>
-  </si>
-  <si>
-    <t>Verificar registos na base de dados</t>
-  </si>
-  <si>
-    <t>Registos armazenados com sucesso</t>
-  </si>
-  <si>
-    <t>Consulta à base de dados</t>
-  </si>
-  <si>
     <t>X -&gt; númerar os requisitos</t>
   </si>
   <si>
-    <t>RF07</t>
-  </si>
-  <si>
-    <t>RF08</t>
-  </si>
-  <si>
-    <t>RF09</t>
-  </si>
-  <si>
-    <t>RF06</t>
-  </si>
-  <si>
-    <t>RF13</t>
-  </si>
-  <si>
     <t>RF04</t>
   </si>
   <si>
-    <t>RNF01</t>
-  </si>
-  <si>
     <t>RF05</t>
+  </si>
+  <si>
+    <t>Componente</t>
+  </si>
+  <si>
+    <t>Configuração</t>
+  </si>
+  <si>
+    <t>Processador</t>
+  </si>
+  <si>
+    <t>Memória RAM</t>
+  </si>
+  <si>
+    <t>Sistema Operativo</t>
+  </si>
+  <si>
+    <t>Armazenamento</t>
+  </si>
+  <si>
+    <t>Intel® Core™ i5-12500H</t>
+  </si>
+  <si>
+    <t>16 GB</t>
+  </si>
+  <si>
+    <t>Windows 11 64 bits</t>
+  </si>
+  <si>
+    <t>SSD</t>
+  </si>
+  <si>
+    <t>Hardware</t>
+  </si>
+  <si>
+    <t>Software</t>
+  </si>
+  <si>
+    <t>Python</t>
+  </si>
+  <si>
+    <t>FastAPI</t>
+  </si>
+  <si>
+    <t>Uvicorn</t>
+  </si>
+  <si>
+    <t>PostgreSQL</t>
+  </si>
+  <si>
+    <t>Visual Studio Code</t>
+  </si>
+  <si>
+    <t>Google Chrome</t>
+  </si>
+  <si>
+    <t>Swagger UI</t>
+  </si>
+  <si>
+    <t>3.14.3</t>
+  </si>
+  <si>
+    <t>0.135.2</t>
+  </si>
+  <si>
+    <t>0.42.0</t>
+  </si>
+  <si>
+    <t>15.8</t>
+  </si>
+  <si>
+    <t>Ferramentas</t>
+  </si>
+  <si>
+    <t>Utilização</t>
+  </si>
+  <si>
+    <t>Teste dos endpoints da API</t>
+  </si>
+  <si>
+    <t>Consulta e validação da base de dados PostgreSQL</t>
+  </si>
+  <si>
+    <t>APIs externas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">APIs </t>
+  </si>
+  <si>
+    <t>Informação</t>
+  </si>
+  <si>
+    <t>IPMA</t>
+  </si>
+  <si>
+    <t>Foreca</t>
+  </si>
+  <si>
+    <t>Open-Meteo</t>
+  </si>
+  <si>
+    <t>OpenWeather</t>
+  </si>
+  <si>
+    <t>Observações, previsões terrestres e previsões marítimas</t>
+  </si>
+  <si>
+    <t>Observações meteorológicas</t>
+  </si>
+  <si>
+    <t>Previsões terrestres e marítimas</t>
+  </si>
+  <si>
+    <t>Previsões terrestres</t>
+  </si>
+  <si>
+    <t>Previsões marítimas</t>
+  </si>
+  <si>
+    <t>Backend</t>
+  </si>
+  <si>
+    <t>Frontend</t>
+  </si>
+  <si>
+    <t>Base de Dados</t>
+  </si>
+  <si>
+    <t>Orquestração</t>
+  </si>
+  <si>
+    <t>APIs Externas</t>
+  </si>
+  <si>
+    <t>FastAPI executado num contentor Docker</t>
+  </si>
+  <si>
+    <t>Aplicação Web executada num contentor Docker</t>
+  </si>
+  <si>
+    <t>Versão</t>
+  </si>
+  <si>
+    <t>Desenvolvimento da aplicação</t>
+  </si>
+  <si>
+    <t>WorldWeatherOnline</t>
+  </si>
+  <si>
+    <t>Docker Compose</t>
+  </si>
+  <si>
+    <t>PostgreSQL executado num contentor Docker</t>
+  </si>
+  <si>
+    <t>DBeaver</t>
+  </si>
+  <si>
+    <t>Execução da interface Web e realização dos testes funcionais</t>
+  </si>
+  <si>
+    <t>Consultadas em tempo real durante os testes</t>
+  </si>
+  <si>
+    <t>ESTG Leiria</t>
+  </si>
+  <si>
+    <t>Peniche</t>
+  </si>
+  <si>
+    <t>39.7351</t>
+  </si>
+  <si>
+    <t>-8.8212</t>
+  </si>
+  <si>
+    <t>Latitude</t>
+  </si>
+  <si>
+    <t>Longitude</t>
+  </si>
+  <si>
+    <t>Bidoeira de Cima</t>
+  </si>
+  <si>
+    <t>39.8426</t>
+  </si>
+  <si>
+    <t>-8.7433</t>
+  </si>
+  <si>
+    <t>São Pedro de Moel</t>
+  </si>
+  <si>
+    <t>Pedrógão Grande</t>
+  </si>
+  <si>
+    <t>Caranguejeira</t>
+  </si>
+  <si>
+    <t>39.7447</t>
+  </si>
+  <si>
+    <t>-8.6912</t>
+  </si>
+  <si>
+    <t>39.7669</t>
+  </si>
+  <si>
+    <t>-9.0198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Localização (Terra) </t>
+  </si>
+  <si>
+    <t>39.9194</t>
+  </si>
+  <si>
+    <t>-8.1333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Localização (MAR) </t>
+  </si>
+  <si>
+    <t>Vieira / Pedrógão</t>
+  </si>
+  <si>
+    <t>39.9300</t>
+  </si>
+  <si>
+    <t>-9.1200</t>
+  </si>
+  <si>
+    <t>39.7300</t>
+  </si>
+  <si>
+    <t>-9.1800</t>
+  </si>
+  <si>
+    <t>Figueira da Foz</t>
+  </si>
+  <si>
+    <t>40.1234</t>
+  </si>
+  <si>
+    <t>-9.0556</t>
+  </si>
+  <si>
+    <t>39.4100</t>
+  </si>
+  <si>
+    <t>-9.5200</t>
+  </si>
+  <si>
+    <t>Consultar observações em diferentes localizações</t>
+  </si>
+  <si>
+    <t>RF01,RF07</t>
+  </si>
+  <si>
+    <t>Tipo de informação</t>
+  </si>
+  <si>
+    <t>Frequência de recolha</t>
+  </si>
+  <si>
+    <t>Previsões Terrestres</t>
+  </si>
+  <si>
+    <t>A cada 30 minutos</t>
+  </si>
+  <si>
+    <t>A cada 1 hora</t>
+  </si>
+  <si>
+    <t>Recolhas diárias</t>
+  </si>
+  <si>
+    <t>RF02,RF08</t>
+  </si>
+  <si>
+    <t>RF03,RF09</t>
+  </si>
+  <si>
+    <t>RF06,RF11</t>
+  </si>
+  <si>
+    <t>RF12,RF13</t>
+  </si>
+  <si>
+    <t>Consultar previsões terrestres em diferentes localizações</t>
+  </si>
+  <si>
+    <t>Consulta ao Dbeaver</t>
+  </si>
+  <si>
+    <t>Exemplo antes/depois</t>
+  </si>
+  <si>
+    <t>Comparar a resposta original da API com os dados normalizados</t>
+  </si>
+  <si>
+    <t>Verificar os registos na base de dados</t>
+  </si>
+  <si>
+    <t>A informação é apresentada lado a lado e identifica a respetiva fonte</t>
+  </si>
+  <si>
+    <t>Comparar os dados da mesma localização entre diferentes APIs</t>
+  </si>
+  <si>
+    <t>Consultar histórico para 24 horas e 7 dias</t>
+  </si>
+  <si>
+    <t>Capturas de ecrã e gráficos</t>
+  </si>
+  <si>
+    <t>Consultar previsões marítimas em diferentes localizações costeiras</t>
+  </si>
+  <si>
+    <t>RFN01</t>
+  </si>
+  <si>
+    <t>Tabelas e gráficos.</t>
+  </si>
+  <si>
+    <t>Executar pedidos repetidos aos endpoints.</t>
+  </si>
+  <si>
+    <t>Nº de localizações com observações apresentadas corretamente</t>
+  </si>
+  <si>
+    <t>Nº de localizações com previsões apresentadas corretamente</t>
+  </si>
+  <si>
+    <t>Nº de localizações marítimas com previsões apresentadas corretamente</t>
+  </si>
+  <si>
+    <t>Nº de períodos históricos consultados com sucesso</t>
+  </si>
+  <si>
+    <t>Nº de APIs apresentadas e comparadas</t>
+  </si>
+  <si>
+    <t>Latência média, mínima e máxima dos pedidos</t>
+  </si>
+  <si>
+    <t>Nº de respostas normalizadas validadas</t>
+  </si>
+  <si>
+    <t>Apresentação correta das previsões terrestres</t>
+  </si>
+  <si>
+    <t>Apresentação correta das observações para a localização selecionada</t>
+  </si>
+  <si>
+    <t>Apresentação correta das previsões marítimas</t>
+  </si>
+  <si>
+    <t>Nº de registos armazenados na base de dados</t>
+  </si>
+  <si>
+    <t>Apresentação correta do histórico para os períodos disponíveis</t>
+  </si>
+  <si>
+    <t>Os dados normalizados seguem a estrutura definida pelo sistema</t>
+  </si>
+  <si>
+    <t>Armazenamento correto dos dados recolhidos na base de dados</t>
+  </si>
+  <si>
+    <t>Tempos de resposta compatíveis com aplicações interativas</t>
+  </si>
+  <si>
+    <t>Endpoint</t>
+  </si>
+  <si>
+    <t>Localizações utilizadas</t>
+  </si>
+  <si>
+    <t>Pedidos realizados</t>
+  </si>
+  <si>
+    <t>Latência média (ms)</t>
+  </si>
+  <si>
+    <t>Latência mínima (ms)</t>
+  </si>
+  <si>
+    <t>Latência máxima (ms)</t>
+  </si>
+  <si>
+    <t>Erros</t>
+  </si>
+  <si>
+    <t>Taxa de erro</t>
+  </si>
+  <si>
+    <t>/data/observations/current</t>
+  </si>
+  <si>
+    <t>/data/forecast/terrestrial/current</t>
+  </si>
+  <si>
+    <t>/data/forecast/marine/current</t>
+  </si>
+  <si>
+    <t>/data/forecast/terrestrial/history</t>
+  </si>
+  <si>
+    <t>/data/forecast/marine/timeline</t>
+  </si>
+  <si>
+    <t>/data/forecast/terrestrial/records</t>
+  </si>
+  <si>
+    <t>N/A</t>
+  </si>
+  <si>
+    <t>2000/dia</t>
+  </si>
+  <si>
+    <t>3000/minuto</t>
+  </si>
+  <si>
+    <t>100/dia</t>
+  </si>
+  <si>
+    <t>Limite Pedidos</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="5">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -194,8 +531,27 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial Unicode MS"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -208,8 +564,20 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -232,32 +600,257 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="54">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -538,210 +1131,799 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="C4:I15"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="D3:I15"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="4" max="4" width="25" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.42578125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="33.140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="28.42578125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="29.140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.85546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="33" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="28.140625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="28.7109375" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="17.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="4" spans="3:9" x14ac:dyDescent="0.25">
-      <c r="D4" s="2" t="s">
+    <row r="3" spans="4:9" ht="15.75" thickBot="1"/>
+    <row r="4" spans="4:9">
+      <c r="D4" s="34" t="s">
         <v>0</v>
       </c>
-      <c r="E4" s="2" t="s">
+      <c r="E4" s="35" t="s">
         <v>1</v>
       </c>
-      <c r="F4" s="2" t="s">
+      <c r="F4" s="35" t="s">
         <v>2</v>
       </c>
-      <c r="G4" s="2" t="s">
+      <c r="G4" s="35" t="s">
         <v>3</v>
       </c>
-      <c r="H4" s="2" t="s">
+      <c r="H4" s="35" t="s">
         <v>4</v>
       </c>
-      <c r="I4" s="2" t="s">
+      <c r="I4" s="36" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="3:9" ht="30" x14ac:dyDescent="0.25">
-      <c r="D5" s="1" t="s">
+    <row r="5" spans="4:9" ht="45">
+      <c r="D5" s="37" t="s">
         <v>6</v>
       </c>
+      <c r="E5" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="H5" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="I5" s="38" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6" spans="4:9" ht="45">
+      <c r="D6" s="37" t="s">
+        <v>8</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="H6" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="I6" s="38" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="7" spans="4:9" ht="45">
+      <c r="D7" s="37" t="s">
+        <v>9</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="H7" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="I7" s="38" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="8" spans="4:9" ht="30">
+      <c r="D8" s="37" t="s">
+        <v>10</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="H8" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="I8" s="38" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="9" spans="4:9" ht="45">
+      <c r="D9" s="37" t="s">
+        <v>11</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="G9" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="H9" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="I9" s="38" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="10" spans="4:9" ht="45">
+      <c r="D10" s="37" t="s">
+        <v>13</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="G10" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="H10" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="I10" s="38" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="11" spans="4:9" ht="30">
+      <c r="D11" s="37" t="s">
+        <v>14</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="G11" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="H11" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="I11" s="38" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="12" spans="4:9" ht="30.75" thickBot="1">
+      <c r="D12" s="39" t="s">
+        <v>12</v>
+      </c>
+      <c r="E12" s="40" t="s">
+        <v>124</v>
+      </c>
+      <c r="F12" s="41" t="s">
+        <v>141</v>
+      </c>
+      <c r="G12" s="41" t="s">
+        <v>126</v>
+      </c>
+      <c r="H12" s="41" t="s">
+        <v>132</v>
+      </c>
+      <c r="I12" s="42" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="15" spans="4:9">
+      <c r="D15" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2D4CFBF6-8F55-4048-BE53-6A499CCBEFE3}">
+  <dimension ref="D2:W36"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="4" max="4" width="18" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="44.85546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.85546875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="27" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="20.85546875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="15.28515625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="17.85546875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="56.140625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="30" customWidth="1"/>
+    <col min="17" max="17" width="20.42578125" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="52.140625" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.28515625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="4:19">
+      <c r="D2" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="M2" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="Q2" s="2" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="3" spans="4:19" ht="15.75" thickBot="1"/>
+    <row r="4" spans="4:19">
+      <c r="D4" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="E4" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="I4" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="J4" s="11" t="s">
+        <v>64</v>
+      </c>
+      <c r="M4" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="N4" s="11" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q4" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="R4" s="21" t="s">
+        <v>47</v>
+      </c>
+      <c r="S4" s="11" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="5" spans="4:19">
+      <c r="D5" s="4" t="s">
+        <v>20</v>
+      </c>
       <c r="E5" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="F5" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="I5" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="J5" s="13" t="s">
+        <v>37</v>
+      </c>
+      <c r="M5" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="N5" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="Q5" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="R5" s="18" t="s">
+        <v>52</v>
+      </c>
+      <c r="S5" s="51" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="6" spans="4:19" ht="15.75">
+      <c r="D6" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="I6" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="J6" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="M6" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="N6" s="16" t="s">
+        <v>44</v>
+      </c>
+      <c r="Q6" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="R6" s="18" t="s">
+        <v>53</v>
+      </c>
+      <c r="S6" s="52" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="7" spans="4:19">
+      <c r="D7" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="I7" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="J7" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="M7" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="N7" s="16" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q7" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="R7" s="18" t="s">
+        <v>54</v>
+      </c>
+      <c r="S7" s="51" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="8" spans="4:19" ht="15.75" thickBot="1">
+      <c r="D8" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="E8" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="I8" s="14" t="s">
+        <v>33</v>
+      </c>
+      <c r="J8" s="15" t="s">
+        <v>40</v>
+      </c>
+      <c r="M8" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="N8" s="17" t="s">
+        <v>70</v>
+      </c>
+      <c r="Q8" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="R8" s="18" t="s">
+        <v>55</v>
+      </c>
+      <c r="S8" s="51" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="9" spans="4:19" ht="16.5" thickBot="1">
+      <c r="Q9" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="R9" s="24" t="s">
+        <v>56</v>
+      </c>
+      <c r="S9" s="53" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="10" spans="4:19">
+      <c r="M10" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="N10" s="16" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="11" spans="4:19" ht="15.75" thickBot="1">
+      <c r="M11" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="N11" s="17" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="12" spans="4:19" ht="15.75" thickBot="1"/>
+    <row r="13" spans="4:19">
+      <c r="D13" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="E13" s="11" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="14" spans="4:19">
+      <c r="D14" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="E14" s="16" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="15" spans="4:19">
+      <c r="D15" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="E15" s="16" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="16" spans="4:19" ht="15.75" thickBot="1">
+      <c r="D16" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="E16" s="16" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="17" spans="4:23" ht="45">
+      <c r="D17" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="E17" s="16" t="s">
+        <v>67</v>
+      </c>
+      <c r="P17" s="43" t="s">
+        <v>142</v>
+      </c>
+      <c r="Q17" s="44" t="s">
+        <v>143</v>
+      </c>
+      <c r="R17" s="44" t="s">
+        <v>144</v>
+      </c>
+      <c r="S17" s="44" t="s">
+        <v>145</v>
+      </c>
+      <c r="T17" s="44" t="s">
+        <v>146</v>
+      </c>
+      <c r="U17" s="44" t="s">
+        <v>147</v>
+      </c>
+      <c r="V17" s="44" t="s">
+        <v>148</v>
+      </c>
+      <c r="W17" s="45" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="18" spans="4:23" ht="15.75" thickBot="1">
+      <c r="D18" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="E18" s="17" t="s">
+        <v>71</v>
+      </c>
+      <c r="P18" s="49" t="s">
+        <v>150</v>
+      </c>
+      <c r="Q18" s="33">
+        <v>12</v>
+      </c>
+      <c r="R18" s="33">
+        <v>60</v>
+      </c>
+      <c r="S18" s="33">
+        <v>31.75</v>
+      </c>
+      <c r="T18" s="33">
+        <v>24.13</v>
+      </c>
+      <c r="U18" s="33">
+        <v>275.24</v>
+      </c>
+      <c r="V18" s="33">
+        <v>0</v>
+      </c>
+      <c r="W18" s="46">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="4:23" ht="25.5">
+      <c r="P19" s="49" t="s">
+        <v>151</v>
+      </c>
+      <c r="Q19" s="33">
+        <v>12</v>
+      </c>
+      <c r="R19" s="33">
+        <v>60</v>
+      </c>
+      <c r="S19" s="33">
+        <v>181.1</v>
+      </c>
+      <c r="T19" s="33">
+        <v>150.38</v>
+      </c>
+      <c r="U19" s="33">
+        <v>597.61</v>
+      </c>
+      <c r="V19" s="33">
+        <v>0</v>
+      </c>
+      <c r="W19" s="46">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="4:23">
+      <c r="P20" s="49" t="s">
+        <v>152</v>
+      </c>
+      <c r="Q20" s="33">
         <v>7</v>
       </c>
-      <c r="G5" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="H5" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="I5" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="6" spans="3:9" ht="30" x14ac:dyDescent="0.25">
-      <c r="D6" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="E6" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="F6" s="1" t="s">
+      <c r="R20" s="33">
+        <v>60</v>
+      </c>
+      <c r="S20" s="33">
+        <v>100.74</v>
+      </c>
+      <c r="T20" s="33">
+        <v>88.77</v>
+      </c>
+      <c r="U20" s="33">
+        <v>136.96</v>
+      </c>
+      <c r="V20" s="33">
+        <v>0</v>
+      </c>
+      <c r="W20" s="46">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="4:23">
+      <c r="P21" s="49" t="s">
+        <v>153</v>
+      </c>
+      <c r="Q21" s="33">
         <v>12</v>
       </c>
-      <c r="G6" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="H6" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="I6" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="7" spans="3:9" ht="30" x14ac:dyDescent="0.25">
-      <c r="D7" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="E7" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="F7" s="1" t="s">
+      <c r="R21" s="33">
+        <v>60</v>
+      </c>
+      <c r="S21" s="33">
+        <v>127.43</v>
+      </c>
+      <c r="T21" s="33">
+        <v>102.89</v>
+      </c>
+      <c r="U21" s="33">
+        <v>197.78</v>
+      </c>
+      <c r="V21" s="33">
+        <v>0</v>
+      </c>
+      <c r="W21" s="46">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="4:23" ht="15.75" thickBot="1">
+      <c r="P22" s="49" t="s">
+        <v>154</v>
+      </c>
+      <c r="Q22" s="33">
+        <v>7</v>
+      </c>
+      <c r="R22" s="33">
+        <v>60</v>
+      </c>
+      <c r="S22" s="33">
+        <v>107.17</v>
+      </c>
+      <c r="T22" s="33">
+        <v>92.24</v>
+      </c>
+      <c r="U22" s="33">
+        <v>184.86</v>
+      </c>
+      <c r="V22" s="33">
+        <v>0</v>
+      </c>
+      <c r="W22" s="46">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="4:23" ht="26.25" thickBot="1">
+      <c r="D23" s="10" t="s">
+        <v>88</v>
+      </c>
+      <c r="E23" s="21" t="s">
+        <v>76</v>
+      </c>
+      <c r="F23" s="11" t="s">
+        <v>77</v>
+      </c>
+      <c r="I23" s="26" t="s">
+        <v>104</v>
+      </c>
+      <c r="J23" s="27" t="s">
+        <v>105</v>
+      </c>
+      <c r="K23" s="28" t="s">
+        <v>109</v>
+      </c>
+      <c r="P23" s="50" t="s">
+        <v>155</v>
+      </c>
+      <c r="Q23" s="47">
         <v>12</v>
       </c>
-      <c r="G7" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="H7" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="I7" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="8" spans="3:9" ht="45" x14ac:dyDescent="0.25">
-      <c r="D8" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="E8" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="F8" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="G8" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="H8" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="I8" s="1" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="9" spans="3:9" ht="30" x14ac:dyDescent="0.25">
-      <c r="D9" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E9" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="F9" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="G9" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="H9" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="I9" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="10" spans="3:9" ht="30" x14ac:dyDescent="0.25">
-      <c r="D10" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="E10" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="F10" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="G10" s="1" t="s">
+      <c r="R23" s="47">
+        <v>60</v>
+      </c>
+      <c r="S23" s="47">
+        <v>153.86000000000001</v>
+      </c>
+      <c r="T23" s="47">
+        <v>125.35</v>
+      </c>
+      <c r="U23" s="47">
+        <v>196.93</v>
+      </c>
+      <c r="V23" s="47">
+        <v>0</v>
+      </c>
+      <c r="W23" s="48">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="4:23">
+      <c r="D24" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="E24" s="18" t="s">
+        <v>74</v>
+      </c>
+      <c r="F24" s="22" t="s">
+        <v>75</v>
+      </c>
+      <c r="I24" s="29" t="s">
+        <v>53</v>
+      </c>
+      <c r="J24" s="30" t="s">
+        <v>107</v>
+      </c>
+      <c r="K24" s="5">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="25" spans="4:23">
+      <c r="D25" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="E25" s="18" t="s">
+        <v>79</v>
+      </c>
+      <c r="F25" s="22" t="s">
+        <v>80</v>
+      </c>
+      <c r="I25" s="29" t="s">
+        <v>106</v>
+      </c>
+      <c r="J25" s="30" t="s">
+        <v>108</v>
+      </c>
+      <c r="K25" s="5">
         <v>24</v>
       </c>
-      <c r="H10" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="I10" s="1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="11" spans="3:9" ht="30" x14ac:dyDescent="0.25">
-      <c r="D11" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="E11" s="7" t="s">
-        <v>46</v>
-      </c>
-      <c r="F11" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="G11" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="H11" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="I11" s="6" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="12" spans="3:9" ht="30" x14ac:dyDescent="0.25">
-      <c r="D12" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="E12" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="F12" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="G12" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="H12" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="I12" s="6" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="13" spans="3:9" x14ac:dyDescent="0.25">
-      <c r="C13" s="8"/>
-      <c r="D13" s="8"/>
-      <c r="E13" s="8"/>
-      <c r="F13" s="8"/>
-      <c r="G13" s="8"/>
-      <c r="H13" s="8"/>
-      <c r="I13" s="8"/>
-    </row>
-    <row r="15" spans="3:9" x14ac:dyDescent="0.25">
-      <c r="D15" s="4" t="s">
-        <v>40</v>
-      </c>
+    </row>
+    <row r="26" spans="4:23" ht="15.75" thickBot="1">
+      <c r="D26" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="E26" s="19" t="s">
+        <v>86</v>
+      </c>
+      <c r="F26" s="23" t="s">
+        <v>87</v>
+      </c>
+      <c r="I26" s="31" t="s">
+        <v>56</v>
+      </c>
+      <c r="J26" s="32" t="s">
+        <v>108</v>
+      </c>
+      <c r="K26" s="7">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="27" spans="4:23">
+      <c r="D27" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="E27" s="18" t="s">
+        <v>89</v>
+      </c>
+      <c r="F27" s="23" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="28" spans="4:23" ht="15.75" thickBot="1">
+      <c r="D28" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="E28" s="24" t="s">
+        <v>84</v>
+      </c>
+      <c r="F28" s="25" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="30" spans="4:23" ht="15.75" thickBot="1"/>
+    <row r="31" spans="4:23">
+      <c r="D31" s="10" t="s">
+        <v>91</v>
+      </c>
+      <c r="E31" s="21" t="s">
+        <v>76</v>
+      </c>
+      <c r="F31" s="11" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="32" spans="4:23">
+      <c r="D32" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="E32" s="18" t="s">
+        <v>93</v>
+      </c>
+      <c r="F32" s="22" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="33" spans="4:6">
+      <c r="D33" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="E33" s="18" t="s">
+        <v>95</v>
+      </c>
+      <c r="F33" s="22" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="34" spans="4:6">
+      <c r="D34" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="E34" s="19" t="s">
+        <v>98</v>
+      </c>
+      <c r="F34" s="23" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="35" spans="4:6" ht="15.75" thickBot="1">
+      <c r="D35" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="E35" s="24" t="s">
+        <v>100</v>
+      </c>
+      <c r="F35" s="25" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="36" spans="4:6">
+      <c r="F36" s="20"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
